--- a/_ForDRA/BVSimulationFiles/80.xlsx
+++ b/_ForDRA/BVSimulationFiles/80.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.001610017889087657</v>
+        <v>0.03220035778175314</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00160807098635543</v>
+        <v>0.0321614197271086</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001606126437901547</v>
+        <v>0.03212252875803094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001604184240879112</v>
+        <v>0.03208368481758224</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001602244392444675</v>
+        <v>0.0320448878488935</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001600306889758221</v>
+        <v>0.03200613779516442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001598371729983172</v>
+        <v>0.03196743459966344</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001596438910286379</v>
+        <v>0.03192877820572758</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001594508427838118</v>
+        <v>0.03189016855676235</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001592580279812088</v>
+        <v>0.03185160559624176</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001590654463385406</v>
+        <v>0.03181308926770812</v>
       </c>
       <c r="M2" t="n">
-        <v>0.001588730975738602</v>
+        <v>0.03177461951477203</v>
       </c>
       <c r="N2" t="n">
-        <v>0.001586809814055615</v>
+        <v>0.0317361962811123</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00158489097552379</v>
+        <v>0.0316978195104758</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001582974457333872</v>
+        <v>0.03165948914667744</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.001581060256680005</v>
+        <v>0.0316212051336001</v>
       </c>
       <c r="R2" t="n">
-        <v>0.001579148370759725</v>
+        <v>0.0315829674151945</v>
       </c>
       <c r="S2" t="n">
-        <v>0.001577238796773957</v>
+        <v>0.03154477593547914</v>
       </c>
       <c r="T2" t="n">
-        <v>0.00157533153192701</v>
+        <v>0.0315066306385402</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001573426573426574</v>
+        <v>0.03146853146853148</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.001610017889087657</v>
+        <v>0.03220035778175314</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00160807098635543</v>
+        <v>0.0321614197271086</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001606126437901547</v>
+        <v>0.03212252875803094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001604184240879112</v>
+        <v>0.03208368481758224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602244392444675</v>
+        <v>0.0320448878488935</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001600306889758221</v>
+        <v>0.03200613779516442</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001598371729983172</v>
+        <v>0.03196743459966344</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001596438910286379</v>
+        <v>0.03192877820572758</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001594508427838118</v>
+        <v>0.03189016855676235</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001592580279812088</v>
+        <v>0.03185160559624176</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001590654463385406</v>
+        <v>0.03181308926770812</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001588730975738602</v>
+        <v>0.03177461951477203</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001586809814055615</v>
+        <v>0.0317361962811123</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00158489097552379</v>
+        <v>0.0316978195104758</v>
       </c>
       <c r="P3" t="n">
-        <v>0.001582974457333872</v>
+        <v>0.03165948914667744</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001581060256680005</v>
+        <v>0.0316212051336001</v>
       </c>
       <c r="R3" t="n">
-        <v>0.001579148370759725</v>
+        <v>0.0315829674151945</v>
       </c>
       <c r="S3" t="n">
-        <v>0.001577238796773957</v>
+        <v>0.03154477593547914</v>
       </c>
       <c r="T3" t="n">
-        <v>0.00157533153192701</v>
+        <v>0.0315066306385402</v>
       </c>
       <c r="U3" t="n">
-        <v>0.001573426573426574</v>
+        <v>0.03146853146853148</v>
       </c>
     </row>
   </sheetData>
